--- a/docs/import_templates/technoflow_import_template_opportunities.xlsx
+++ b/docs/import_templates/technoflow_import_template_opportunities.xlsx
@@ -722,7 +722,7 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Won, Lost, Initial Discussion, Requirements Gathering, Technical Assessment, Proposal Preparation, Proposal Submitted, Negotiation</t>
+          <t>Won, Lost, Qualification, Requirements Gathering, Technical Assessment, Proposal, Proposal Submitted, Negotiation</t>
         </is>
       </c>
     </row>
